--- a/Sajjad data/by_country_and_state/USA/AL.xlsx
+++ b/Sajjad data/by_country_and_state/USA/AL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="456">
   <si>
     <t>Business Name</t>
   </si>
@@ -89,6 +89,1296 @@
   </si>
   <si>
     <t>2026-10-25T09:08:00.684Z</t>
+  </si>
+  <si>
+    <t>Huntsville Dental Center.</t>
+  </si>
+  <si>
+    <t>(833) 880-2130</t>
+  </si>
+  <si>
+    <t>7224 Governors W, Huntsville, AL 35806</t>
+  </si>
+  <si>
+    <t>Huntsville</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>SundayOpen 24 hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Huntsville+Dental+Center./data=!4m7!3m6!1s0x88626ee971d2e861:0xd5a070e2c56563!8m2!3d34.7034573!4d-86.6868863!16s%2Fg%2F1tsykxzn!19sChIJYejSceluYogRY2XF4nCg1QA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:12:31.936Z</t>
+  </si>
+  <si>
+    <t>1800 Dentist Huntsville</t>
+  </si>
+  <si>
+    <t>(541) 514-1731</t>
+  </si>
+  <si>
+    <t>Dental clinic</t>
+  </si>
+  <si>
+    <t>2516a Sparkman Dr NW, Huntsville, AL 35810</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Sunday9 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/1800+Dentist+Huntsville/data=!4m7!3m6!1s0x88626b18150936a9:0x8fd89db832e9c3ca!8m2!3d34.7637232!4d-86.5953101!16s%2Fg%2F11ykwbn5k5!19sChIJqTYJFRhrYogRysPpMrid2I8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:12:33.809Z</t>
+  </si>
+  <si>
+    <t>Dr. William S. Callahan, DDS.</t>
+  </si>
+  <si>
+    <t>(256) 885-0225</t>
+  </si>
+  <si>
+    <t>2045 Cecil Ashburn Dr SE #203, Huntsville, AL 35802</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+William+S.+Callahan,+DDS./data=!4m7!3m6!1s0x88621257020989f3:0x75055f402e089c16!8m2!3d34.6723134!4d-86.5372261!16s%2Fg%2F1tpllgh1!19sChIJ84kJAlcSYogRFpwILkBfBXU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:12:43.929Z</t>
+  </si>
+  <si>
+    <t>Mountain View Family Dentistry. Center</t>
+  </si>
+  <si>
+    <t>(256) 533-2746</t>
+  </si>
+  <si>
+    <t>110 Woodside Dr, Owens Cross Roads, AL 35763</t>
+  </si>
+  <si>
+    <t>Owens Cross Roads</t>
+  </si>
+  <si>
+    <t>Sunday9 AM–2 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mountain+View+Family+Dentistry.+Center/data=!4m7!3m6!1s0x8862118ce5165b2d:0x269d119e33e76191!8m2!3d34.6597908!4d-86.4924324!16s%2Fg%2F1tg2f6np!19sChIJLVsW5YwRYogRkWHnM54RnSY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:14:23.879Z</t>
+  </si>
+  <si>
+    <t>Toneys Family Dentistry.</t>
+  </si>
+  <si>
+    <t>(256) 852-6161</t>
+  </si>
+  <si>
+    <t>2585 Sparkman Dr NW Ste Ab, Huntsville, AL 35810</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Toneys+Family+Dentistry./data=!4m7!3m6!1s0x88626b23a8adb387:0xb111305094c4e7dc!8m2!3d34.7630892!4d-86.5976763!16s%2Fg%2F1tfsckzl!19sChIJh7OtqCNrYogR3OfElFAwEbE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:14:26.030Z</t>
+  </si>
+  <si>
+    <t>Providence Family Dental: Terry Jamelah A MD</t>
+  </si>
+  <si>
+    <t>(256) 489-5640</t>
+  </si>
+  <si>
+    <t>475 Providence Main St NW Unit 301, Huntsville, AL 35806</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Providence+Family+Dental:+Terry+Jamelah+A+MD/data=!4m7!3m6!1s0x88626919cf19de35:0x771375c1220bd675!8m2!3d34.754851!4d-86.6919449!16s%2Fg%2F1tfk9rl0!19sChIJNd4ZzxlpYogRddYLIsF1E3c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:14:28.122Z</t>
+  </si>
+  <si>
+    <t>Russell H. Lowrey, D.M.D., P.C.</t>
+  </si>
+  <si>
+    <t>(256) 536-9635</t>
+  </si>
+  <si>
+    <t>Orthodontist</t>
+  </si>
+  <si>
+    <t>1111 Gleneagles Dr SW, Huntsville, AL 35801</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Russell+H.+Lowrey,+D.M.D.,+P.C./data=!4m7!3m6!1s0x8862135209b0cbdd:0x72812b99a6177b70!8m2!3d34.693164!4d-86.5800925!16s%2Fg%2F1tf5fgts!19sChIJ3cuwCVITYogRcHsXppkrgXI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:15:12.009Z</t>
+  </si>
+  <si>
+    <t>Tracie M Battle, DMD</t>
+  </si>
+  <si>
+    <t>(256) 867-1399</t>
+  </si>
+  <si>
+    <t>807 Regal Dr SW, Huntsville, AL 35801</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tracie+M+Battle,+DMD/data=!4m7!3m6!1s0x8862154a5679638d:0x7daa2778b294583!8m2!3d34.7091934!4d-86.5870553!16s%2Fg%2F1tdx9f81!19sChIJjWN5VkoVYogRg0Upi3ei2gc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:15:15.112Z</t>
+  </si>
+  <si>
+    <t>Dr. Paul R. Weeks, DMD</t>
+  </si>
+  <si>
+    <t>(256) 883-4032</t>
+  </si>
+  <si>
+    <t>Dental implants periodontist</t>
+  </si>
+  <si>
+    <t>4032 Balmoral Dr SW, Huntsville, AL 35801</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>SundayClosed; MondayClosed; Tuesday7:30 AM–4:30 PM; Wednesday7:30 AM–4:30 PM; Thursday7:30 AM–4:30 PM; Friday7:30 AM–4:30 PM; SaturdayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Paul+R.+Weeks,+DMD/data=!4m7!3m6!1s0x88621332e9e54c8f:0xbef7ff4806cf7cd9!8m2!3d34.6948832!4d-86.5791587!16s%2Fg%2F1tfj3x66!19sChIJj0zl6TITYogR2XzPBkj_974?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:15:28.822Z</t>
+  </si>
+  <si>
+    <t>Aesthetic and Implant Dentistry of North Alabama</t>
+  </si>
+  <si>
+    <t>(256) 883-7832</t>
+  </si>
+  <si>
+    <t>2227 Drake Ave SW, Huntsville, AL 35805</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aesthetic+and+Implant+Dentistry+of+North+Alabama/data=!4m7!3m6!1s0x88626cea2483ffff:0xcc9a4ae7f0b2aaca!8m2!3d34.6998273!4d-86.6016949!16s%2Fg%2F11t13s64fp!19sChIJ__-DJOpsYogRyqqy8OdKmsw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:15:33.933Z</t>
+  </si>
+  <si>
+    <t>Dr. Mark A. Ralph, DMD</t>
+  </si>
+  <si>
+    <t>(256) 533-3735</t>
+  </si>
+  <si>
+    <t>2353 Whitesburg Dr SE, Huntsville, AL 35801</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Mark+A.+Ralph,+DMD/data=!4m7!3m6!1s0x8862134e6c3ab6ab:0x66a769cefb54efe9!8m2!3d34.713373!4d-86.57457!16s%2Fg%2F1tfcjh9k!19sChIJq7Y6bE4TYogR6e9U-85pp2Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:15:55.325Z</t>
+  </si>
+  <si>
+    <t>Reynolds Drew D DDS</t>
+  </si>
+  <si>
+    <t>(256) 536-4951</t>
+  </si>
+  <si>
+    <t>600 St Clair Ave SW # 19, Huntsville, AL 35801</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>SundayClosed; Monday8 AM–4:30 PM; Tuesday8 AM–4:30 PM; Wednesday8 AM–4:30 PM; Thursday8 AM–4:30 PM; FridayClosed; SaturdayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Reynolds+Drew+D+DDS/data=!4m7!3m6!1s0x88626ca91bc40755:0xe786bd236d5ba0be!8m2!3d34.722733!4d-86.587608!16s%2Fg%2F1td5mffq!19sChIJVQfEG6lsYogRvqBbbSO9huc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:16:50.393Z</t>
+  </si>
+  <si>
+    <t>Reasner Dental</t>
+  </si>
+  <si>
+    <t>(205) 595-2626</t>
+  </si>
+  <si>
+    <t>924 Montclair Rd #101, Birmingham, AL 35213</t>
+  </si>
+  <si>
+    <t>Birmingham</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Reasner+Dental/data=!4m7!3m6!1s0x88891a7791298b3f:0xde1888e37dd3a9ec!8m2!3d33.5185057!4d-86.7425672!16s%2Fg%2F1tf_j57v!19sChIJP4spkXcaiYgR7KnTfeOIGN4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:17:05.215Z</t>
+  </si>
+  <si>
+    <t>StoneCreek Dental Care - Trussville</t>
+  </si>
+  <si>
+    <t>(205) 853-3643</t>
+  </si>
+  <si>
+    <t>5590 Chalkville Mountain Rd # A, Birmingham, AL 35235</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/StoneCreek+Dental+Care+-+Trussville/data=!4m7!3m6!1s0x88890c71fb0d868b:0xa08108dad8d4f9ab!8m2!3d33.6507151!4d-86.6353971!16s%2Fg%2F1tdr8z96!19sChIJi4YN-3EMiYgRq_nU2NoIgaA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:17:07.053Z</t>
+  </si>
+  <si>
+    <t>Reeves Cosmetic Dentistry At Greystone</t>
+  </si>
+  <si>
+    <t>(251) 485-0572</t>
+  </si>
+  <si>
+    <t>Cosmetic dentist</t>
+  </si>
+  <si>
+    <t>8040 Hugh Daniel Dr, Birmingham, AL 35242</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Reeves+Cosmetic+Dentistry+At+Greystone/data=!4m7!3m6!1s0x888915b903873e2d:0xbee1a81baebff478!8m2!3d33.4167521!4d-86.6584905!16s%2Fg%2F1tdwqw8x!19sChIJLT6HA7kViYgRePS_rhuo4b4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:18:17.238Z</t>
+  </si>
+  <si>
+    <t>Woods Jr Eddie DDS..</t>
+  </si>
+  <si>
+    <t>(205) 251-0186</t>
+  </si>
+  <si>
+    <t>101 6th Ave S, Birmingham, AL 35205</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Woods+Jr+Eddie+DDS../data=!4m7!3m6!1s0x88891c040f73e599:0x15048d1231f5484e!8m2!3d33.4936678!4d-86.8268598!16s%2Fg%2F1tdcs96r!19sChIJmeVzDwQciYgRTkj1MRKNBBU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:18:20.442Z</t>
+  </si>
+  <si>
+    <t>Ford, Alfred DMD</t>
+  </si>
+  <si>
+    <t>(205) 591-8325</t>
+  </si>
+  <si>
+    <t>6 61st St N, Birmingham, AL 35212</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ford,+Alfred+DMD/data=!4m7!3m6!1s0x88891a9c7cc3cf6f:0x7819833634744220!8m2!3d33.5445033!4d-86.746002!16s%2Fg%2F1tmqgzrs!19sChIJb8_DfJwaiYgRIEJ0NDaDGXg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:18:47.397Z</t>
+  </si>
+  <si>
+    <t>Brighter Image Dentistry</t>
+  </si>
+  <si>
+    <t>(205) 591-6220</t>
+  </si>
+  <si>
+    <t>2908 Central Ave #150, Homewood, AL 35209</t>
+  </si>
+  <si>
+    <t>Homewood</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Brighter+Image+Dentistry/data=!4m7!3m6!1s0x88891965cd58a431:0xc26b074c55fbd304!8m2!3d33.478425!4d-86.796267!16s%2Fg%2F11b6q466zq!19sChIJMaRYzWUZiYgRBNP7VUwHa8I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:19:19.175Z</t>
+  </si>
+  <si>
+    <t>Just Kids Dental</t>
+  </si>
+  <si>
+    <t>(205) 251-1010</t>
+  </si>
+  <si>
+    <t>Pediatric dentist</t>
+  </si>
+  <si>
+    <t>2320 7th Ave S b, Birmingham, AL 35233</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Just+Kids+Dental/data=!4m7!3m6!1s0x88891bc77b2857ed:0x3fb55375dbc0f3bb!8m2!3d33.508453!4d-86.7949229!16s%2Fg%2F11cjk4ddvt!19sChIJ7Vcoe8cbiYgRu_PA23VTtT8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:19:38.563Z</t>
+  </si>
+  <si>
+    <t>Dr. Janice G. Jackson, DMD</t>
+  </si>
+  <si>
+    <t>(205) 939-5174</t>
+  </si>
+  <si>
+    <t>1600 7th Ave S, Birmingham, AL 35233</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Janice+G.+Jackson,+DMD/data=!4m7!3m6!1s0x88891be961b81a47:0xac29de69a263330e!8m2!3d33.5024887!4d-86.8061066!16s%2Fg%2F1tykw4mp!19sChIJRxq4YekbiYgRDjNjomneKaw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:19:40.311Z</t>
+  </si>
+  <si>
+    <t>Childrens Dental Center</t>
+  </si>
+  <si>
+    <t>(205) 939-4912</t>
+  </si>
+  <si>
+    <t>1801 14th Ave S, Birmingham, AL 35205</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Childrens+Dental+Center/data=!4m7!3m6!1s0x88891bdb6bb67f6f:0x9604aaad5aa892a1!8m2!3d33.496253!4d-86.7960641!16s%2Fg%2F1tfr15x3!19sChIJb3-2a9sbiYgRoZKoWq2qBJY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:19:42.958Z</t>
+  </si>
+  <si>
+    <t>Dr. Stephen C. Mitchell, DMD</t>
+  </si>
+  <si>
+    <t>(205) 934-1136</t>
+  </si>
+  <si>
+    <t>1919 7th Ave S, Birmingham, AL 35233</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Stephen+C.+Mitchell,+DMD/data=!4m7!3m6!1s0x88891bc1c1621411:0x4a53225e3a64660f!8m2!3d33.505299!4d-86.800972!16s%2Fg%2F1tgcn1d9!19sChIJERRiwcEbiYgRD2ZkOl4iU0o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:19:44.684Z</t>
+  </si>
+  <si>
+    <t>Odum Patrick DDS</t>
+  </si>
+  <si>
+    <t>(205) 251-8557</t>
+  </si>
+  <si>
+    <t>2228 1st Ave N #200, Birmingham, AL 35203</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Odum+Patrick+DDS/data=!4m7!3m6!1s0x88891bbd8a38e333:0xe141d1d482d6b1e5!8m2!3d33.5165678!4d-86.8018365!16s%2Fg%2F1tdn9fsk!19sChIJM-M4ir0biYgR5bHWgtTRQeE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:19:46.579Z</t>
+  </si>
+  <si>
+    <t>Jerome C Scales Pa</t>
+  </si>
+  <si>
+    <t>(205) 781-9399</t>
+  </si>
+  <si>
+    <t>623 8th Ave W, Birmingham, AL 35204</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jerome+C+Scales+Pa/data=!4m7!3m6!1s0x88891c40b49ed681:0xc6d0fbce6ce2d2c2!8m2!3d33.5114863!4d-86.847017!16s%2Fg%2F1tfq9_fx!19sChIJgdaetEAciYgRwtLibM770MY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:19:48.321Z</t>
+  </si>
+  <si>
+    <t>Urgent Dentist Point</t>
+  </si>
+  <si>
+    <t>(659) 260-5066</t>
+  </si>
+  <si>
+    <t>Emergency dental service</t>
+  </si>
+  <si>
+    <t>4342 Vanderbilt Rd, Birmingham, AL 35217</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgent+Dentist+Point/data=!4m7!3m6!1s0x88891b4af082d267:0xa458358991507f8c!8m2!3d33.5671529!4d-86.7838885!16s%2Fg%2F11p1rfflrh!19sChIJZ9KC8EobiYgRjH9QkYk1WKQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:20:13.762Z</t>
+  </si>
+  <si>
+    <t>Quick Dental Now</t>
+  </si>
+  <si>
+    <t>(205) 839-0331</t>
+  </si>
+  <si>
+    <t>1812 3rd Ave S, Birmingham, AL 35233</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Quick+Dental+Now/data=!4m7!3m6!1s0x88891b7744443ea7:0x682c771c1f482442!8m2!3d33.5091956!4d-86.8049128!16s%2Fg%2F11zf5vdt1y!19sChIJpz5ERHcbiYgRQiRIHxx3LGg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:20:15.411Z</t>
+  </si>
+  <si>
+    <t>Quick Dental Gateway</t>
+  </si>
+  <si>
+    <t>(659) 786-0067</t>
+  </si>
+  <si>
+    <t>5505 1st Ave N, Birmingham, AL 35212</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Quick+Dental+Gateway/data=!4m7!3m6!1s0x88891bf25778823d:0x8e19c6b3a6a1f546!8m2!3d33.539715!4d-86.752519!16s%2Fg%2F11p1rfbq6t!19sChIJPYJ4V_IbiYgRRvWhprPGGY4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:20:17.657Z</t>
+  </si>
+  <si>
+    <t>Park Place Dentistry</t>
+  </si>
+  <si>
+    <t>(205) 323-0454</t>
+  </si>
+  <si>
+    <t>2001 Park Pl #835, Birmingham, AL 35203</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Park+Place+Dentistry/data=!4m7!3m6!1s0x88891b905e1a4325:0x7e2fca8b99a7a13c!8m2!3d33.5201932!4d-86.808269!16s%2Fg%2F11d_v2t7f3!19sChIJJUMaXpAbiYgRPKGnmYvKL34?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:20:21.277Z</t>
+  </si>
+  <si>
+    <t>AmeriPlan Dental and Health Plans</t>
+  </si>
+  <si>
+    <t>(205) 216-2770</t>
+  </si>
+  <si>
+    <t>JAFFE &amp; ERDBERG LAND TITLE BUILDING, 603 19th St N, Birmingham, AL 35203</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/AmeriPlan+Dental+and+Health+Plans/data=!4m7!3m6!1s0x88891b90ffffffff:0xc52ee072167f05f2!8m2!3d33.5188536!4d-86.8103091!16s%2Fg%2F1v2yzmqr!19sChIJ_____5AbiYgR8gV_FnLgLsU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:20:23.174Z</t>
+  </si>
+  <si>
+    <t>Pignataro James DDS</t>
+  </si>
+  <si>
+    <t>(205) 251-8128</t>
+  </si>
+  <si>
+    <t>2930 4th Ave S, Birmingham, AL 35233</t>
+  </si>
+  <si>
+    <t>Sunday12–3 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pignataro+James+DDS/data=!4m7!3m6!1s0x88891bb13b2724bd:0x8119c6dfb20cda09!8m2!3d33.515634!4d-86.789004!16s%2Fg%2F1hbpwsb_k!19sChIJvSQnO7EbiYgRCdoMst_GGYE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:20:25.872Z</t>
+  </si>
+  <si>
+    <t>Dr. James E. Roberts, DMD</t>
+  </si>
+  <si>
+    <t>(205) 933-9333</t>
+  </si>
+  <si>
+    <t>2301 Arlington Ave S, Birmingham, AL 35205</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+James+E.+Roberts,+DMD/data=!4m7!3m6!1s0x88891bce6977259f:0xd07d42dffe36f969!8m2!3d33.4996219!4d-86.7880846!16s%2Fg%2F1tftxqsr!19sChIJnyV3ac4biYgRafk2_t9CfdA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:21:20.511Z</t>
+  </si>
+  <si>
+    <t>Dr. Ann F. Drummond, DMD</t>
+  </si>
+  <si>
+    <t>(205) 988-0363</t>
+  </si>
+  <si>
+    <t>3825 Lorna Rd #210, Birmingham, AL 35244</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Ann+F.+Drummond,+DMD/data=!4m7!3m6!1s0x8889223c34944cef:0xee84e8bba3626226!8m2!3d33.372134!4d-86.807968!16s%2Fg%2F1tfpw0p2!19sChIJ70yUNDwiiYgRJmJio7vohO4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:21:22.176Z</t>
+  </si>
+  <si>
+    <t>Dr. Amy M. Anderson, DMD</t>
+  </si>
+  <si>
+    <t>(334) 279-0760</t>
+  </si>
+  <si>
+    <t>4790 Woodmere Blvd, Montgomery, AL 36106</t>
+  </si>
+  <si>
+    <t>Montgomery</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Amy+M.+Anderson,+DMD/data=!4m7!3m6!1s0x888c2a503e5b9741:0xe5024c35020099e5!8m2!3d32.3550836!4d-86.2245495!16s%2Fg%2F1tdpgzr8!19sChIJQZdbPlAqjIgR5ZkAAjVMAuU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:21:36.477Z</t>
+  </si>
+  <si>
+    <t>MAO Dental Clinic</t>
+  </si>
+  <si>
+    <t>(334) 239-9704</t>
+  </si>
+  <si>
+    <t>3052 McGehee Rd, Montgomery, AL 36111</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/MAO+Dental+Clinic/data=!4m7!3m6!1s0x888e8028579ed609:0x509f0897cf1cda8!8m2!3d32.3375646!4d-86.2577908!16s%2Fg%2F11d_8tdmn4!19sChIJCdaeVyiAjogRqM3xfInwCQU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:21:38.683Z</t>
+  </si>
+  <si>
+    <t>Toothbuds at Lagoon Park LLC</t>
+  </si>
+  <si>
+    <t>(844) 595-2940</t>
+  </si>
+  <si>
+    <t>553 N Eastern Blvd, Montgomery, AL 36117</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>Sunday7 AM–7 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Toothbuds+at+Lagoon+Park+LLC/data=!4m7!3m6!1s0x888c2bc93a0dd031:0x9fdeabfd5d4e0766!8m2!3d32.3994412!4d-86.212843!16s%2Fg%2F11c1p4y33r!19sChIJMdANOskrjIgRZgdOXf2r3p8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:21:40.455Z</t>
+  </si>
+  <si>
+    <t>Donated Dental Services.</t>
+  </si>
+  <si>
+    <t>(334) 834-1114</t>
+  </si>
+  <si>
+    <t>Montgomery, AL 36101</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Donated+Dental+Services./data=!4m7!3m6!1s0x888e816c5d454007:0xd50ad695b7a6cdc5!8m2!3d32.3738766!4d-86.3110236!16s%2Fg%2F1261fzswt!19sChIJB0BFXWyBjogRxc2mt5XWCtU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:21:42.370Z</t>
+  </si>
+  <si>
+    <t>Dental Clinic Montgomery</t>
+  </si>
+  <si>
+    <t>(866) 227-3192</t>
+  </si>
+  <si>
+    <t>211 Catoma St, Montgomery, AL 36104</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Clinic+Montgomery/data=!4m7!3m6!1s0x888e8122d632dd6f:0xf49c405616562584!8m2!3d32.3757464!4d-86.3132114!16s%2Fg%2F11vks4srcn!19sChIJb90y1iKBjogRhCVWFlZAnPQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:21:44.374Z</t>
+  </si>
+  <si>
+    <t>Dr. Kent D. Hill, DDS</t>
+  </si>
+  <si>
+    <t>(334) 613-0626</t>
+  </si>
+  <si>
+    <t>2920 Marti Ln, Montgomery, AL 36116</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Kent+D.+Hill,+DDS/data=!4m7!3m6!1s0x888c2a9fab75666f:0x8aa0bd091a0dc1a2!8m2!3d32.3269357!4d-86.2539004!16s%2Fg%2F1tf4ftff!19sChIJb2Z1q58qjIgRosENGgm9oIo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:21:46.238Z</t>
+  </si>
+  <si>
+    <t>MAFB Medical Clinic./</t>
+  </si>
+  <si>
+    <t>(334) 953-3368</t>
+  </si>
+  <si>
+    <t>Medical clinic</t>
+  </si>
+  <si>
+    <t>300 Twining St, Montgomery, AL 36113</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/MAFB+Medical+Clinic.%2F/data=!4m7!3m6!1s0x888e86b73c5bfdb9:0xc15d2add4122cf70!8m2!3d32.3759427!4d-86.3457139!16s%2Fg%2F11c1782ft_!19sChIJuf1bPLeGjogRcM8iQd0qXcE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:21:48.070Z</t>
+  </si>
+  <si>
+    <t>Bennett &amp; Lumpkin DMD</t>
+  </si>
+  <si>
+    <t>(334) 272-3776</t>
+  </si>
+  <si>
+    <t>4270 Carmichael Rd, Montgomery, AL 36106</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bennett+%26+Lumpkin+DMD/data=!4m7!3m6!1s0x888c2a448ee50af7:0x493b033da9adf97c!8m2!3d32.3588739!4d-86.2301967!16s%2Fg%2F1tfgklfl!19sChIJ9wrljkQqjIgRfPmtqT0DO0k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:21:49.894Z</t>
+  </si>
+  <si>
+    <t>Dale Entrekin, DMD, PC</t>
+  </si>
+  <si>
+    <t>(334) 271-3111</t>
+  </si>
+  <si>
+    <t>7022 Vaughn Rd, Montgomery, AL 36116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dale+Entrekin,+DMD,+PC/data=!4m7!3m6!1s0x888c2b747887a6bd:0x324c7c590d6fb0ff!8m2!3d32.3386867!4d-86.1920336!16s%2Fg%2F1tzlzr25!19sChIJvaaHeHQrjIgR_7BvDVl8TDI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:21:51.837Z</t>
+  </si>
+  <si>
+    <t>Central Dental Studio Inc</t>
+  </si>
+  <si>
+    <t>(334) 264-0138</t>
+  </si>
+  <si>
+    <t>Dental laboratory</t>
+  </si>
+  <si>
+    <t>837 S Perry St, Montgomery, AL 36104</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Central+Dental+Studio+Inc/data=!4m7!3m6!1s0x888e810df1ffbe81:0xa130ded3b89743de!8m2!3d32.3655673!4d-86.3066199!16s%2Fg%2F1tjmff74!19sChIJgb7_8Q2BjogR3kOXuNPeMKE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:21:54.218Z</t>
+  </si>
+  <si>
+    <t>Jones Robert S PC: Jones Melodie A DDS</t>
+  </si>
+  <si>
+    <t>(334) 277-5666</t>
+  </si>
+  <si>
+    <t>4130 Carmichael Way Ste A, Montgomery, AL 36106</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jones+Robert+S+PC:+Jones+Melodie+A+DDS/data=!4m7!3m6!1s0x888c2a6600367661:0xa2984e0d35a4b726!8m2!3d32.3568004!4d-86.2409443!16s%2Fg%2F1tlc8vff!19sChIJYXY2AGYqjIgRJrekNQ1OmKI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:22:57.790Z</t>
+  </si>
+  <si>
+    <t>Waters Forrest E Dr</t>
+  </si>
+  <si>
+    <t>(334) 281-2451</t>
+  </si>
+  <si>
+    <t>3150 Zelda Ct, Montgomery, AL 36106</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Waters+Forrest+E+Dr/data=!4m7!3m6!1s0x888e81db9dbbb005:0x2d6765f41990a008!8m2!3d32.3624605!4d-86.2640241!16s%2Fg%2F1tfwqrbg!19sChIJBbC7nduBjogRCKCQGfRlZy0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:23:00.131Z</t>
+  </si>
+  <si>
+    <t>Clarence Steineker</t>
+  </si>
+  <si>
+    <t>(334) 277-5665</t>
+  </si>
+  <si>
+    <t>4730 Woodmere Blvd, Montgomery, AL 36106</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clarence+Steineker/data=!4m7!3m6!1s0x888c2a5acbafffff:0xc537c75d99c76bfc!8m2!3d32.3563324!4d-86.2275065!16s%2Fg%2F11sh2bfpbl!19sChIJ__-vy1oqjIgR_GvHmV3HN8U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:23:24.444Z</t>
+  </si>
+  <si>
+    <t>Dr. R. Bruce Sansom D.M.D.</t>
+  </si>
+  <si>
+    <t>(334) 279-0808</t>
+  </si>
+  <si>
+    <t>4001 Carmichael Rd #205, Montgomery, AL 36106</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+R.+Bruce+Sansom+D.M.D./data=!4m7!3m6!1s0x888e81da8cade0eb:0x4c39d4101508cee4!8m2!3d32.3576136!4d-86.242923!16s%2Fg%2F1tv24xyz!19sChIJ6-CtjNqBjogR5M4IFRDUOUw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:23:27.683Z</t>
+  </si>
+  <si>
+    <t>Roosevelt A Daniel PC</t>
+  </si>
+  <si>
+    <t>(334) 834-9647</t>
+  </si>
+  <si>
+    <t>524 E Edgemont Ave, Montgomery, AL 36111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Roosevelt+A+Daniel+PC/data=!4m7!3m6!1s0x888e80ffa7788aff:0x9dc05591e183aa4e!8m2!3d32.3443676!4d-86.2988891!16s%2Fg%2F1tfrbz19!19sChIJ_4p4p_-AjogRTqqD4ZFVwJ0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:23:29.568Z</t>
+  </si>
+  <si>
+    <t>T S Family Cosmetic &amp; Implant</t>
+  </si>
+  <si>
+    <t>(334) 279-6488</t>
+  </si>
+  <si>
+    <t>8161A Seaton Pl, Montgomery, AL 36116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/T+S+Family+Cosmetic+%26+Implant/data=!4m7!3m6!1s0x888c2c815f771b47:0xd67a22aaa4fe1ca!8m2!3d32.3383538!4d-86.1713901!16s%2Fg%2F1tgtg853!19sChIJRxt3X4EsjIgRyuFPqiqiZw0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:23:31.375Z</t>
+  </si>
+  <si>
+    <t>Dr. Forrest Harris</t>
+  </si>
+  <si>
+    <t>(334) 396-0222</t>
+  </si>
+  <si>
+    <t>1551 E Trinity Blvd, Montgomery, AL 36106</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Forrest+Harris/data=!4m7!3m6!1s0x888c2a43226eaaab:0x7f1707f9079da4f6!8m2!3d32.3580517!4d-86.2332175!16s%2Fg%2F11qgb79mdz!19sChIJq6puIkMqjIgR9qSdB_kHF38?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:23:33.307Z</t>
+  </si>
+  <si>
+    <t>Dr. S K. Dunn, DMD</t>
+  </si>
+  <si>
+    <t>(334) 270-1044</t>
+  </si>
+  <si>
+    <t>7051 Halcyon Summit Dr, Montgomery, AL 36117</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+S+K.+Dunn,+DMD/data=!4m7!3m6!1s0x888c2a662bd71973:0x2fb634cb343650f1!8m2!3d32.3684727!4d-86.1698061!16s%2Fg%2F1v2ky5zm!19sChIJcxnXK2YqjIgR8VA2NMs0ti8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:24:16.209Z</t>
+  </si>
+  <si>
+    <t>Leonard Wayne Yarbrough</t>
+  </si>
+  <si>
+    <t>(334) 272-7900</t>
+  </si>
+  <si>
+    <t>1220 Carmichael Way, Montgomery, AL 36106</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Leonard+Wayne+Yarbrough/data=!4m7!3m6!1s0x888c2a6606fc4745:0x4c7a92473794b688!8m2!3d32.3564346!4d-86.2410821!16s%2Fg%2F11ty7v57pd!19sChIJRUf8BmYqjIgRiLaUN0eSekw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:24:37.895Z</t>
+  </si>
+  <si>
+    <t>Burke Dianne E DDS.</t>
+  </si>
+  <si>
+    <t>(334) 271-0423</t>
+  </si>
+  <si>
+    <t>2101 Eastern Blvd #410, Montgomery, AL 36117</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Burke+Dianne+E+DDS./data=!4m7!3m6!1s0x888c2a5385a9ee7b:0xe89e16463b2cc8d2!8m2!3d32.3515853!4d-86.2175771!16s%2Fg%2F1tg35_7n!19sChIJe-6phVMqjIgR0sgsO0YWnug?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:24:51.942Z</t>
+  </si>
+  <si>
+    <t>J. Larry Gafford, DMD</t>
+  </si>
+  <si>
+    <t>(334) 440-7963</t>
+  </si>
+  <si>
+    <t>4224 Carmichael Rd, Montgomery, AL 36106</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/J.+Larry+Gafford,+DMD/data=!4m7!3m6!1s0x888c2a436d340001:0xe24fd0a662f24ba4!8m2!3d32.3594304!4d-86.2303478!16s%2Fg%2F11h4cgf2l5!19sChIJAQA0bUMqjIgRpEvyYqbQT-I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:25:01.818Z</t>
+  </si>
+  <si>
+    <t>Dental Services Montgomery</t>
+  </si>
+  <si>
+    <t>(866) 204-1443</t>
+  </si>
+  <si>
+    <t>7931 Vaughn Rd, Montgomery, AL 36116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Services+Montgomery/data=!4m7!3m6!1s0x888c2b91e7d6389b:0xeb3fe277867e91d1!8m2!3d32.339101!4d-86.1778766!16s%2Fg%2F11l6zzrjq3!19sChIJmzjW55ErjIgR0ZF-hnfiP-s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:25:15.641Z</t>
+  </si>
+  <si>
+    <t>Sculpted by Monroe Body Contouring and Yoni Spa</t>
+  </si>
+  <si>
+    <t>(334) 440-2164</t>
+  </si>
+  <si>
+    <t>Body shaping class</t>
+  </si>
+  <si>
+    <t>3500 Eastdale Cir, Montgomery, AL 36117</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sculpted+by+Monroe+Body+Contouring+and+Yoni+Spa/data=!4m7!3m6!1s0x888c2bbf36f08a29:0x470c4f79f0e5534f!8m2!3d32.3843002!4d-86.2023292!16s%2Fg%2F11qgjycvsq!19sChIJKYrwNr8rjIgRT1Pl8HlPDEc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:25:43.909Z</t>
+  </si>
+  <si>
+    <t>Mobile Bay Dental - The Shoppes at Bel Air</t>
+  </si>
+  <si>
+    <t>(251) 301-6555</t>
+  </si>
+  <si>
+    <t>3281 Joe Treadwell Dr Ste G18A, Mobile, AL 36606</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mobile+Bay+Dental+-+The+Shoppes+at+Bel+Air/data=!4m7!3m6!1s0x889a4da199c510dd:0x11032007d7790b69!8m2!3d30.673485!4d-88.1231517!16s%2Fg%2F11c2k3qwrw!19sChIJ3RDFmaFNmogRaQt51wcgAxE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:26:12.883Z</t>
+  </si>
+  <si>
+    <t>Prime Dental Emergency</t>
+  </si>
+  <si>
+    <t>(401) 293-1122</t>
+  </si>
+  <si>
+    <t>119 S Ann St, Mobile, AL 36604</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Prime+Dental+Emergency/data=!4m7!3m6!1s0x889a4ff30088ab23:0xcb38bd428a162a43!8m2!3d30.6830264!4d-88.0660597!16s%2Fg%2F11y4491xqq!19sChIJI6uIAPNPmogRQyoWikK9OMs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:26:45.372Z</t>
+  </si>
+  <si>
+    <t>Hillcrest Dental Care, Dr. Carrie Tombrello DMD</t>
+  </si>
+  <si>
+    <t>(251) 776-6878</t>
+  </si>
+  <si>
+    <t>1100 Hillcrest Rd # A, Mobile, AL 36695</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hillcrest+Dental+Care,+Dr.+Carrie+Tombrello+DMD/data=!4m7!3m6!1s0x889bb2e8eaf41117:0xdb59c51e2345a7a8!8m2!3d30.6665245!4d-88.1911811!16s%2Fg%2F1tftxr5g!19sChIJFxH06uiym4gRqKdFIx7FWds?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:26:51.055Z</t>
+  </si>
+  <si>
+    <t>Tillman's Corner Dental</t>
+  </si>
+  <si>
+    <t>(251) 660-1400</t>
+  </si>
+  <si>
+    <t>5659 Three Notch Rd, Mobile, AL 36619</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tillman%27s+Corner+Dental/data=!4m7!3m6!1s0x889bb4b6a16ceda1:0xf8535111d0564ead!8m2!3d30.5887874!4d-88.1732451!16s%2Fg%2F1tggv95f!19sChIJoe1soba0m4gRrU5W0BFRU_g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:27:06.907Z</t>
+  </si>
+  <si>
+    <t>SENIOR DENTAL CARE OF ALABAMA</t>
+  </si>
+  <si>
+    <t>(251) 545-4885</t>
+  </si>
+  <si>
+    <t>2783 Lynndell Dr, Mobile, AL 36695</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/SENIOR+DENTAL+CARE+OF+ALABAMA/data=!4m7!3m6!1s0x889bb3ceded72533:0xe5023751d1715699!8m2!3d30.6330592!4d-88.2106876!16s%2Fg%2F11fsn583q5!19sChIJMyXX3s6zm4gRmVZx0VE3AuU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:27:08.762Z</t>
+  </si>
+  <si>
+    <t>Dr Gerald White</t>
+  </si>
+  <si>
+    <t>(251) 633-8411</t>
+  </si>
+  <si>
+    <t>6164 Omni Park Dr, Mobile, AL 36609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Gerald+White/data=!4m7!3m6!1s0x889bb2e7dedf42bb:0xb8344e149933447a!8m2!3d30.6643423!4d-88.1890408!16s%2Fg%2F1tghqc8f!19sChIJu0Lf3ueym4gRekQzmRRONLg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:27:24.351Z</t>
+  </si>
+  <si>
+    <t>Bayside Dental Associates</t>
+  </si>
+  <si>
+    <t>(251) 476-6966</t>
+  </si>
+  <si>
+    <t>2020 Rosedale Rd, Mobile, AL 36605</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bayside+Dental+Associates/data=!4m7!3m6!1s0x889a4ea3e54e1b3b:0xf4bcc0a51d197392!8m2!3d30.6238837!4d-88.0845634!16s%2Fg%2F1tf6mz_k!19sChIJOxtO5aNOmogRknMZHaXAvPQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:27:29.570Z</t>
+  </si>
+  <si>
+    <t>Johnson Samuel L DDS</t>
+  </si>
+  <si>
+    <t>(251) 639-0911</t>
+  </si>
+  <si>
+    <t>740 Hillcrest Rd #2b, Mobile, AL 36695</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Johnson+Samuel+L+DDS/data=!4m7!3m6!1s0x889bb2ebc5560e51:0x500572e9eea01906!8m2!3d30.6763121!4d-88.1912443!16s%2Fg%2F1vjdqvqc!19sChIJUQ5Wxeuym4gRBhmg7ulyBVA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:27:41.797Z</t>
+  </si>
+  <si>
+    <t>Dr. Gerard Weinacker D.M.D</t>
+  </si>
+  <si>
+    <t>(251) 343-0508</t>
+  </si>
+  <si>
+    <t>6328 Piccadilly Square Dr, Mobile, AL 36609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Gerard+Weinacker+D.M.D/data=!4m7!3m6!1s0x889bb2ea45456dcf:0xf05714f92c9631c0!8m2!3d30.6739043!4d-88.1889813!16s%2Fg%2F1td5s1cb!19sChIJz21FReqym4gRwDGWLPkUV_A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:27:44.151Z</t>
+  </si>
+  <si>
+    <t>Moffett Road Dentistry</t>
+  </si>
+  <si>
+    <t>(251) 342-6672</t>
+  </si>
+  <si>
+    <t>5050 Moffett Rd, Mobile, AL 36618</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Moffett+Road+Dentistry/data=!4m7!3m6!1s0x889a5327f96e1397:0x6d9fa81551c7068f!8m2!3d30.7211779!4d-88.1590855!16s%2Fg%2F11vrj43cdl!19sChIJlxNu-SdTmogRjwbHURWon20?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:28:04.087Z</t>
+  </si>
+  <si>
+    <t>Renew Family Dental</t>
+  </si>
+  <si>
+    <t>(251) 217-2560</t>
+  </si>
+  <si>
+    <t>517 Georgian Dr, Mobile, AL 36609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Renew+Family+Dental/data=!4m7!3m6!1s0x889a4d2d76d00001:0x880457c877263878!8m2!3d30.6636753!4d-88.1659997!16s%2Fg%2F11h5q829xk!19sChIJAQDQdi1NmogReDgmd8hXBIg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:28:06.186Z</t>
+  </si>
+  <si>
+    <t>Family Dentist Center</t>
+  </si>
+  <si>
+    <t>(251) 341-1500</t>
+  </si>
+  <si>
+    <t>6309 Piccadilly Square Dr Ste A, Mobile, AL 36609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Dentist+Center/data=!4m7!3m6!1s0x889bb2ea4d5d7913:0xb946bb498f086628!8m2!3d30.6749188!4d-88.1882!16s%2Fg%2F1td5gxgj!19sChIJE3ldTeqym4gRKGYIj0m7Rrk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:28:08.030Z</t>
+  </si>
+  <si>
+    <t>Dr. Nicholas L. Southall, DMD</t>
+  </si>
+  <si>
+    <t>(251) 666-5113</t>
+  </si>
+  <si>
+    <t>3263 Demetropolis Rd, Mobile, AL 36693</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Nicholas+L.+Southall,+DMD/data=!4m7!3m6!1s0x889a4cba4e823e37:0x16acbb1fbff2c574!8m2!3d30.6222214!4d-88.1561562!16s%2Fg%2F1tld0z4j!19sChIJNz6CTrpMmogRdMXyvx-7rBY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:28:10.516Z</t>
+  </si>
+  <si>
+    <t>Baldy Maureen T DMD</t>
+  </si>
+  <si>
+    <t>(251) 342-3323</t>
+  </si>
+  <si>
+    <t>3920 Airport Blvd B, Mobile, AL 36608</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Baldy+Maureen+T+DMD/data=!4m7!3m6!1s0x889a4d6b425f9677:0xa0655e2fdc59d27b!8m2!3d30.6769941!4d-88.1445764!16s%2Fg%2F1tzvxbq5!19sChIJd5ZfQmtNmogRe9JZ3C9eZaA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:28:12.265Z</t>
+  </si>
+  <si>
+    <t>Cockrell Dental Office, LLC</t>
+  </si>
+  <si>
+    <t>(251) 639-0110</t>
+  </si>
+  <si>
+    <t>1040 Hillcrest Rd, Mobile, AL 36695</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cockrell+Dental+Office,+LLC/data=!4m7!3m6!1s0x889bb2e91d2d8387:0xac45f00e4f11cade!8m2!3d30.66764!4d-88.1911017!16s%2Fg%2F1tcvvm_s!19sChIJh4MtHemym4gR3soRTw7wRaw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:28:38.190Z</t>
+  </si>
+  <si>
+    <t>Azalea City Pediatric Dentistry</t>
+  </si>
+  <si>
+    <t>(251) 300-8881</t>
+  </si>
+  <si>
+    <t>4736 Airport Blvd, Mobile, AL 36608</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Azalea+City+Pediatric+Dentistry/data=!4m7!3m6!1s0x889bb2b7d9bd5359:0x7df8019f66991935!8m2!3d30.6765496!4d-88.176293!16s%2Fg%2F1tgdty0y!19sChIJWVO92beym4gRNRmZZp8B-H0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:28:52.200Z</t>
+  </si>
+  <si>
+    <t>Dr Dougie</t>
+  </si>
+  <si>
+    <t>(251) 660-8603</t>
+  </si>
+  <si>
+    <t>5047 Cottage Hill Rd, Mobile, AL 36609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Dougie/data=!4m7!3m6!1s0x889a4cd768d1e08b:0x2f211700ec6ef5c5!8m2!3d30.6479395!4d-88.1596409!16s%2Fg%2F1tg4m4p8!19sChIJi-DRaNdMmogRxfVu7AAXIS8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:28:54.762Z</t>
+  </si>
+  <si>
+    <t>Mc Murphy Jr Marion B DDS</t>
+  </si>
+  <si>
+    <t>(251) 342-5979</t>
+  </si>
+  <si>
+    <t>4732 Airport Blvd, Mobile, AL 36608</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mc+Murphy+Jr+Marion+B+DDS/data=!4m7!3m6!1s0x889bb2b7d7223d35:0x5081c8e455365a98!8m2!3d30.6767268!4d-88.1759208!16s%2Fg%2F1tffkkgb!19sChIJNT0i17eym4gRmFo2VeTIgVA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:28:56.575Z</t>
+  </si>
+  <si>
+    <t>Dr. Thomas</t>
+  </si>
+  <si>
+    <t>(251) 343-2170</t>
+  </si>
+  <si>
+    <t>801 S University Blvd, Mobile, AL 36609</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Thomas/data=!4m7!3m6!1s0x889bad521e779599:0xe0933dd5b8e3bc95!8m2!3d30.6645808!4d-88.1660713!16s%2Fg%2F11b76twkg1!19sChIJmZV3HlKtm4gRlbzjuNU9k-A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:28:59.648Z</t>
+  </si>
+  <si>
+    <t>Dr. Hubert Parker</t>
+  </si>
+  <si>
+    <t>(251) 634-2341</t>
+  </si>
+  <si>
+    <t>9985 Airport Blvd B, Mobile, AL 36608</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Hubert+Parker/data=!4m7!3m6!1s0x889bb1b116f00001:0xa8f3610d972dd2db!8m2!3d30.6702444!4d-88.2785445!16s%2Fg%2F11rwxg3c31!19sChIJAQDwFrGxm4gR29Itlw1h86g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:29:01.573Z</t>
+  </si>
+  <si>
+    <t>Crawford Lee DDS</t>
+  </si>
+  <si>
+    <t>(251) 661-0282</t>
+  </si>
+  <si>
+    <t>4216 Aurelia St, Mobile, AL 36609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Crawford+Lee+DDS/data=!4m7!3m6!1s0x889a4d294c032353:0x5a741d10e4ced483!8m2!3d30.6584922!4d-88.1624031!16s%2Fg%2F1tw1fm0y!19sChIJUyMDTClNmogRg9TO5BAddFo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:29:03.475Z</t>
+  </si>
+  <si>
+    <t>Dr. Thomas H. Hannahan, DMD</t>
+  </si>
+  <si>
+    <t>(251) 342-1002</t>
+  </si>
+  <si>
+    <t>Endodontist</t>
+  </si>
+  <si>
+    <t>3602 Old Shell Rd # B, Mobile, AL 36608</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Thomas+H.+Hannahan,+DMD/data=!4m7!3m6!1s0x889a527f59c04aeb:0xb96876a0ff8bac41!8m2!3d30.6989799!4d-88.1251056!16s%2Fg%2F1v4ptsnw!19sChIJ60rAWX9SmogRQayL_6B2aLk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T16:29:17.054Z</t>
   </si>
 </sst>
 </file>
@@ -469,7 +1759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -568,6 +1858,3163 @@
         <v>25</v>
       </c>
     </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" t="s">
+        <v>78</v>
+      </c>
+      <c r="M10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" t="s">
+        <v>86</v>
+      </c>
+      <c r="M11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>38</v>
+      </c>
+      <c r="K12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" t="s">
+        <v>91</v>
+      </c>
+      <c r="M12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" t="s">
+        <v>96</v>
+      </c>
+      <c r="M13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" t="s">
+        <v>101</v>
+      </c>
+      <c r="J14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K14" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" t="s">
+        <v>103</v>
+      </c>
+      <c r="M14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" t="s">
+        <v>110</v>
+      </c>
+      <c r="M15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s">
+        <v>71</v>
+      </c>
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>38</v>
+      </c>
+      <c r="K16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" t="s">
+        <v>115</v>
+      </c>
+      <c r="M16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" t="s">
+        <v>121</v>
+      </c>
+      <c r="M17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I18" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" t="s">
+        <v>127</v>
+      </c>
+      <c r="M18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s">
+        <v>132</v>
+      </c>
+      <c r="I19" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" t="s">
+        <v>133</v>
+      </c>
+      <c r="M19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" t="s">
+        <v>138</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" t="s">
+        <v>139</v>
+      </c>
+      <c r="M20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D21" t="s">
+        <v>144</v>
+      </c>
+      <c r="E21" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" t="s">
+        <v>145</v>
+      </c>
+      <c r="M21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" t="s">
+        <v>149</v>
+      </c>
+      <c r="E22" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>150</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" t="s">
+        <v>151</v>
+      </c>
+      <c r="M22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>153</v>
+      </c>
+      <c r="B23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C23" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>156</v>
+      </c>
+      <c r="M23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" t="s">
+        <v>160</v>
+      </c>
+      <c r="E24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>38</v>
+      </c>
+      <c r="I24" t="s">
+        <v>39</v>
+      </c>
+      <c r="J24" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>161</v>
+      </c>
+      <c r="M24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>165</v>
+      </c>
+      <c r="E25" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>46</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>166</v>
+      </c>
+      <c r="M25" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>171</v>
+      </c>
+      <c r="M26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s">
+        <v>38</v>
+      </c>
+      <c r="I27" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" t="s">
+        <v>38</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" t="s">
+        <v>177</v>
+      </c>
+      <c r="M27" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" t="s">
+        <v>175</v>
+      </c>
+      <c r="D28" t="s">
+        <v>181</v>
+      </c>
+      <c r="E28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>38</v>
+      </c>
+      <c r="I28" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" t="s">
+        <v>182</v>
+      </c>
+      <c r="M28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" t="s">
+        <v>175</v>
+      </c>
+      <c r="D29" t="s">
+        <v>186</v>
+      </c>
+      <c r="E29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I29" t="s">
+        <v>39</v>
+      </c>
+      <c r="J29" t="s">
+        <v>38</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" t="s">
+        <v>187</v>
+      </c>
+      <c r="M29" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>189</v>
+      </c>
+      <c r="B30" t="s">
+        <v>190</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s">
+        <v>38</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" t="s">
+        <v>192</v>
+      </c>
+      <c r="M30" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>194</v>
+      </c>
+      <c r="B31" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" t="s">
+        <v>196</v>
+      </c>
+      <c r="E31" t="s">
+        <v>108</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>38</v>
+      </c>
+      <c r="I31" t="s">
+        <v>39</v>
+      </c>
+      <c r="J31" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" t="s">
+        <v>197</v>
+      </c>
+      <c r="M31" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>199</v>
+      </c>
+      <c r="B32" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>201</v>
+      </c>
+      <c r="E32" t="s">
+        <v>108</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>202</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" t="s">
+        <v>203</v>
+      </c>
+      <c r="M32" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>205</v>
+      </c>
+      <c r="B33" t="s">
+        <v>206</v>
+      </c>
+      <c r="C33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E33" t="s">
+        <v>108</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" t="s">
+        <v>208</v>
+      </c>
+      <c r="J33" t="s">
+        <v>38</v>
+      </c>
+      <c r="K33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" t="s">
+        <v>209</v>
+      </c>
+      <c r="M33" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>211</v>
+      </c>
+      <c r="B34" t="s">
+        <v>212</v>
+      </c>
+      <c r="C34" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" t="s">
+        <v>213</v>
+      </c>
+      <c r="E34" t="s">
+        <v>108</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s">
+        <v>214</v>
+      </c>
+      <c r="J34" t="s">
+        <v>38</v>
+      </c>
+      <c r="K34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>215</v>
+      </c>
+      <c r="M34" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>217</v>
+      </c>
+      <c r="B35" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>219</v>
+      </c>
+      <c r="E35" t="s">
+        <v>220</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>221</v>
+      </c>
+      <c r="M35" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>223</v>
+      </c>
+      <c r="B36" t="s">
+        <v>224</v>
+      </c>
+      <c r="C36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" t="s">
+        <v>225</v>
+      </c>
+      <c r="E36" t="s">
+        <v>220</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>226</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>227</v>
+      </c>
+      <c r="M36" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>231</v>
+      </c>
+      <c r="E37" t="s">
+        <v>220</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>232</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>233</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" t="s">
+        <v>234</v>
+      </c>
+      <c r="M37" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>236</v>
+      </c>
+      <c r="B38" t="s">
+        <v>237</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>238</v>
+      </c>
+      <c r="E38" t="s">
+        <v>220</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s">
+        <v>38</v>
+      </c>
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>239</v>
+      </c>
+      <c r="M38" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>241</v>
+      </c>
+      <c r="B39" t="s">
+        <v>242</v>
+      </c>
+      <c r="C39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" t="s">
+        <v>243</v>
+      </c>
+      <c r="E39" t="s">
+        <v>220</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>38</v>
+      </c>
+      <c r="I39" t="s">
+        <v>39</v>
+      </c>
+      <c r="J39" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>244</v>
+      </c>
+      <c r="M39" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>246</v>
+      </c>
+      <c r="B40" t="s">
+        <v>247</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" t="s">
+        <v>248</v>
+      </c>
+      <c r="E40" t="s">
+        <v>220</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>249</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>250</v>
+      </c>
+      <c r="M40" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>252</v>
+      </c>
+      <c r="B41" t="s">
+        <v>253</v>
+      </c>
+      <c r="C41" t="s">
+        <v>254</v>
+      </c>
+      <c r="D41" t="s">
+        <v>255</v>
+      </c>
+      <c r="E41" t="s">
+        <v>220</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>31</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>256</v>
+      </c>
+      <c r="M41" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>258</v>
+      </c>
+      <c r="B42" t="s">
+        <v>259</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>260</v>
+      </c>
+      <c r="E42" t="s">
+        <v>220</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>261</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>22</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>262</v>
+      </c>
+      <c r="M42" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>264</v>
+      </c>
+      <c r="B43" t="s">
+        <v>265</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>266</v>
+      </c>
+      <c r="E43" t="s">
+        <v>220</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s">
+        <v>22</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>267</v>
+      </c>
+      <c r="M43" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>269</v>
+      </c>
+      <c r="B44" t="s">
+        <v>270</v>
+      </c>
+      <c r="C44" t="s">
+        <v>271</v>
+      </c>
+      <c r="D44" t="s">
+        <v>272</v>
+      </c>
+      <c r="E44" t="s">
+        <v>220</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s">
+        <v>38</v>
+      </c>
+      <c r="K44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" t="s">
+        <v>273</v>
+      </c>
+      <c r="M44" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>275</v>
+      </c>
+      <c r="B45" t="s">
+        <v>276</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>277</v>
+      </c>
+      <c r="E45" t="s">
+        <v>220</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s">
+        <v>31</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>278</v>
+      </c>
+      <c r="M45" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>280</v>
+      </c>
+      <c r="B46" t="s">
+        <v>281</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" t="s">
+        <v>282</v>
+      </c>
+      <c r="E46" t="s">
+        <v>220</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s">
+        <v>22</v>
+      </c>
+      <c r="K46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
+        <v>283</v>
+      </c>
+      <c r="M46" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>285</v>
+      </c>
+      <c r="B47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" t="s">
+        <v>287</v>
+      </c>
+      <c r="E47" t="s">
+        <v>220</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>38</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>288</v>
+      </c>
+      <c r="M47" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>290</v>
+      </c>
+      <c r="B48" t="s">
+        <v>291</v>
+      </c>
+      <c r="C48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" t="s">
+        <v>292</v>
+      </c>
+      <c r="E48" t="s">
+        <v>220</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>109</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>293</v>
+      </c>
+      <c r="M48" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>295</v>
+      </c>
+      <c r="B49" t="s">
+        <v>296</v>
+      </c>
+      <c r="C49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" t="s">
+        <v>297</v>
+      </c>
+      <c r="E49" t="s">
+        <v>220</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>126</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s">
+        <v>22</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>298</v>
+      </c>
+      <c r="M49" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>300</v>
+      </c>
+      <c r="B50" t="s">
+        <v>301</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" t="s">
+        <v>302</v>
+      </c>
+      <c r="E50" t="s">
+        <v>220</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>38</v>
+      </c>
+      <c r="I50" t="s">
+        <v>39</v>
+      </c>
+      <c r="J50" t="s">
+        <v>38</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>303</v>
+      </c>
+      <c r="M50" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>305</v>
+      </c>
+      <c r="B51" t="s">
+        <v>306</v>
+      </c>
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>307</v>
+      </c>
+      <c r="E51" t="s">
+        <v>220</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>30</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>38</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>308</v>
+      </c>
+      <c r="M51" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>310</v>
+      </c>
+      <c r="B52" t="s">
+        <v>311</v>
+      </c>
+      <c r="C52" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" t="s">
+        <v>312</v>
+      </c>
+      <c r="E52" t="s">
+        <v>220</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s">
+        <v>38</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>313</v>
+      </c>
+      <c r="M52" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>315</v>
+      </c>
+      <c r="B53" t="s">
+        <v>316</v>
+      </c>
+      <c r="C53" t="s">
+        <v>82</v>
+      </c>
+      <c r="D53" t="s">
+        <v>317</v>
+      </c>
+      <c r="E53" t="s">
+        <v>220</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>38</v>
+      </c>
+      <c r="I53" t="s">
+        <v>208</v>
+      </c>
+      <c r="J53" t="s">
+        <v>38</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
+        <v>318</v>
+      </c>
+      <c r="M53" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>320</v>
+      </c>
+      <c r="B54" t="s">
+        <v>321</v>
+      </c>
+      <c r="C54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" t="s">
+        <v>322</v>
+      </c>
+      <c r="E54" t="s">
+        <v>220</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
+        <v>323</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>233</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>324</v>
+      </c>
+      <c r="M54" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>326</v>
+      </c>
+      <c r="B55" t="s">
+        <v>327</v>
+      </c>
+      <c r="C55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" t="s">
+        <v>328</v>
+      </c>
+      <c r="E55" t="s">
+        <v>220</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s">
+        <v>38</v>
+      </c>
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" t="s">
+        <v>329</v>
+      </c>
+      <c r="M55" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>331</v>
+      </c>
+      <c r="B56" t="s">
+        <v>332</v>
+      </c>
+      <c r="C56" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" t="s">
+        <v>333</v>
+      </c>
+      <c r="E56" t="s">
+        <v>220</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
+        <v>38</v>
+      </c>
+      <c r="I56" t="s">
+        <v>39</v>
+      </c>
+      <c r="J56" t="s">
+        <v>22</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" t="s">
+        <v>334</v>
+      </c>
+      <c r="M56" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>336</v>
+      </c>
+      <c r="B57" t="s">
+        <v>337</v>
+      </c>
+      <c r="C57" t="s">
+        <v>338</v>
+      </c>
+      <c r="D57" t="s">
+        <v>339</v>
+      </c>
+      <c r="E57" t="s">
+        <v>220</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>38</v>
+      </c>
+      <c r="I57" t="s">
+        <v>39</v>
+      </c>
+      <c r="J57" t="s">
+        <v>22</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>340</v>
+      </c>
+      <c r="M57" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>342</v>
+      </c>
+      <c r="B58" t="s">
+        <v>343</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" t="s">
+        <v>344</v>
+      </c>
+      <c r="E58" t="s">
+        <v>345</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" t="s">
+        <v>323</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s">
+        <v>22</v>
+      </c>
+      <c r="K58" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" t="s">
+        <v>346</v>
+      </c>
+      <c r="M58" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>348</v>
+      </c>
+      <c r="B59" t="s">
+        <v>349</v>
+      </c>
+      <c r="C59" t="s">
+        <v>175</v>
+      </c>
+      <c r="D59" t="s">
+        <v>350</v>
+      </c>
+      <c r="E59" t="s">
+        <v>345</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>38</v>
+      </c>
+      <c r="K59" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" t="s">
+        <v>351</v>
+      </c>
+      <c r="M59" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>353</v>
+      </c>
+      <c r="B60" t="s">
+        <v>354</v>
+      </c>
+      <c r="C60" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" t="s">
+        <v>355</v>
+      </c>
+      <c r="E60" t="s">
+        <v>345</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>22</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>356</v>
+      </c>
+      <c r="M60" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>358</v>
+      </c>
+      <c r="B61" t="s">
+        <v>359</v>
+      </c>
+      <c r="C61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" t="s">
+        <v>360</v>
+      </c>
+      <c r="E61" t="s">
+        <v>345</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>323</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>22</v>
+      </c>
+      <c r="K61" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" t="s">
+        <v>361</v>
+      </c>
+      <c r="M61" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>363</v>
+      </c>
+      <c r="B62" t="s">
+        <v>364</v>
+      </c>
+      <c r="C62" t="s">
+        <v>36</v>
+      </c>
+      <c r="D62" t="s">
+        <v>365</v>
+      </c>
+      <c r="E62" t="s">
+        <v>345</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>38</v>
+      </c>
+      <c r="I62" t="s">
+        <v>39</v>
+      </c>
+      <c r="J62" t="s">
+        <v>22</v>
+      </c>
+      <c r="K62" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" t="s">
+        <v>366</v>
+      </c>
+      <c r="M62" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>368</v>
+      </c>
+      <c r="B63" t="s">
+        <v>369</v>
+      </c>
+      <c r="C63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" t="s">
+        <v>370</v>
+      </c>
+      <c r="E63" t="s">
+        <v>345</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>71</v>
+      </c>
+      <c r="I63" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s">
+        <v>31</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>371</v>
+      </c>
+      <c r="M63" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>373</v>
+      </c>
+      <c r="B64" t="s">
+        <v>374</v>
+      </c>
+      <c r="C64" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" t="s">
+        <v>375</v>
+      </c>
+      <c r="E64" t="s">
+        <v>345</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" t="s">
+        <v>376</v>
+      </c>
+      <c r="I64" t="s">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s">
+        <v>22</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" t="s">
+        <v>377</v>
+      </c>
+      <c r="M64" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>379</v>
+      </c>
+      <c r="B65" t="s">
+        <v>380</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" t="s">
+        <v>381</v>
+      </c>
+      <c r="E65" t="s">
+        <v>345</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>46</v>
+      </c>
+      <c r="I65" t="s">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K65" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" t="s">
+        <v>382</v>
+      </c>
+      <c r="M65" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>384</v>
+      </c>
+      <c r="B66" t="s">
+        <v>385</v>
+      </c>
+      <c r="C66" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" t="s">
+        <v>386</v>
+      </c>
+      <c r="E66" t="s">
+        <v>345</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>71</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>22</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" t="s">
+        <v>387</v>
+      </c>
+      <c r="M66" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>389</v>
+      </c>
+      <c r="B67" t="s">
+        <v>390</v>
+      </c>
+      <c r="C67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" t="s">
+        <v>391</v>
+      </c>
+      <c r="E67" t="s">
+        <v>345</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>109</v>
+      </c>
+      <c r="I67" t="s">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" t="s">
+        <v>392</v>
+      </c>
+      <c r="M67" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>394</v>
+      </c>
+      <c r="B68" t="s">
+        <v>395</v>
+      </c>
+      <c r="C68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" t="s">
+        <v>396</v>
+      </c>
+      <c r="E68" t="s">
+        <v>345</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>20</v>
+      </c>
+      <c r="I68" t="s">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s">
+        <v>38</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>397</v>
+      </c>
+      <c r="M68" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>399</v>
+      </c>
+      <c r="B69" t="s">
+        <v>400</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" t="s">
+        <v>401</v>
+      </c>
+      <c r="E69" t="s">
+        <v>345</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" t="s">
+        <v>38</v>
+      </c>
+      <c r="I69" t="s">
+        <v>39</v>
+      </c>
+      <c r="J69" t="s">
+        <v>22</v>
+      </c>
+      <c r="K69" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" t="s">
+        <v>402</v>
+      </c>
+      <c r="M69" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>404</v>
+      </c>
+      <c r="B70" t="s">
+        <v>405</v>
+      </c>
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" t="s">
+        <v>406</v>
+      </c>
+      <c r="E70" t="s">
+        <v>345</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" t="s">
+        <v>20</v>
+      </c>
+      <c r="I70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s">
+        <v>22</v>
+      </c>
+      <c r="K70" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" t="s">
+        <v>407</v>
+      </c>
+      <c r="M70" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>409</v>
+      </c>
+      <c r="B71" t="s">
+        <v>410</v>
+      </c>
+      <c r="C71" t="s">
+        <v>143</v>
+      </c>
+      <c r="D71" t="s">
+        <v>411</v>
+      </c>
+      <c r="E71" t="s">
+        <v>345</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" t="s">
+        <v>126</v>
+      </c>
+      <c r="I71" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s">
+        <v>22</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" t="s">
+        <v>412</v>
+      </c>
+      <c r="M71" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>414</v>
+      </c>
+      <c r="B72" t="s">
+        <v>415</v>
+      </c>
+      <c r="C72" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" t="s">
+        <v>416</v>
+      </c>
+      <c r="E72" t="s">
+        <v>345</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>109</v>
+      </c>
+      <c r="I72" t="s">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s">
+        <v>22</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" t="s">
+        <v>417</v>
+      </c>
+      <c r="M72" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>419</v>
+      </c>
+      <c r="B73" t="s">
+        <v>420</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" t="s">
+        <v>421</v>
+      </c>
+      <c r="E73" t="s">
+        <v>345</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" t="s">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s">
+        <v>22</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" t="s">
+        <v>422</v>
+      </c>
+      <c r="M73" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>424</v>
+      </c>
+      <c r="B74" t="s">
+        <v>425</v>
+      </c>
+      <c r="C74" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" t="s">
+        <v>426</v>
+      </c>
+      <c r="E74" t="s">
+        <v>345</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" t="s">
+        <v>226</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>22</v>
+      </c>
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" t="s">
+        <v>427</v>
+      </c>
+      <c r="M74" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>429</v>
+      </c>
+      <c r="B75" t="s">
+        <v>430</v>
+      </c>
+      <c r="C75" t="s">
+        <v>143</v>
+      </c>
+      <c r="D75" t="s">
+        <v>431</v>
+      </c>
+      <c r="E75" t="s">
+        <v>345</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>22</v>
+      </c>
+      <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" t="s">
+        <v>432</v>
+      </c>
+      <c r="M75" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>434</v>
+      </c>
+      <c r="B76" t="s">
+        <v>435</v>
+      </c>
+      <c r="C76" t="s">
+        <v>143</v>
+      </c>
+      <c r="D76" t="s">
+        <v>436</v>
+      </c>
+      <c r="E76" t="s">
+        <v>345</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s">
+        <v>437</v>
+      </c>
+      <c r="I76" t="s">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s">
+        <v>38</v>
+      </c>
+      <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" t="s">
+        <v>438</v>
+      </c>
+      <c r="M76" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>440</v>
+      </c>
+      <c r="B77" t="s">
+        <v>441</v>
+      </c>
+      <c r="C77" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" t="s">
+        <v>442</v>
+      </c>
+      <c r="E77" t="s">
+        <v>345</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>20</v>
+      </c>
+      <c r="I77" t="s">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s">
+        <v>38</v>
+      </c>
+      <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" t="s">
+        <v>443</v>
+      </c>
+      <c r="M77" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>445</v>
+      </c>
+      <c r="B78" t="s">
+        <v>446</v>
+      </c>
+      <c r="C78" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" t="s">
+        <v>447</v>
+      </c>
+      <c r="E78" t="s">
+        <v>345</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" t="s">
+        <v>132</v>
+      </c>
+      <c r="I78" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s">
+        <v>38</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>448</v>
+      </c>
+      <c r="M78" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>450</v>
+      </c>
+      <c r="B79" t="s">
+        <v>451</v>
+      </c>
+      <c r="C79" t="s">
+        <v>452</v>
+      </c>
+      <c r="D79" t="s">
+        <v>453</v>
+      </c>
+      <c r="E79" t="s">
+        <v>345</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>323</v>
+      </c>
+      <c r="I79" t="s">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s">
+        <v>38</v>
+      </c>
+      <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
+        <v>454</v>
+      </c>
+      <c r="M79" t="s">
+        <v>455</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/Sajjad data/by_country_and_state/USA/AL.xlsx
+++ b/Sajjad data/by_country_and_state/USA/AL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="517">
   <si>
     <t>Business Name</t>
   </si>
@@ -1379,6 +1379,189 @@
   </si>
   <si>
     <t>2026-10-25T16:29:17.054Z</t>
+  </si>
+  <si>
+    <t>Tuscaloosa Pediatric Dentistry</t>
+  </si>
+  <si>
+    <t>(205) 556-6100</t>
+  </si>
+  <si>
+    <t>2415 Veterans Memorial Pkwy, Tuscaloosa, AL 35404</t>
+  </si>
+  <si>
+    <t>Tuscaloosa</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tuscaloosa+Pediatric+Dentistry/data=!4m7!3m6!1s0x8888a851192ebab7:0x688f22f8fba94668!8m2!3d33.1971157!4d-87.5065495!16s%2Fg%2F1tx8tzt2!19sChIJt7ouGVGoiIgRaEap-_gij2g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:47:08.727Z</t>
+  </si>
+  <si>
+    <t>Belinda Rhodes</t>
+  </si>
+  <si>
+    <t>(205) 344-9220</t>
+  </si>
+  <si>
+    <t>6000 Old Greensboro Rd, Tuscaloosa, AL 35405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Belinda+Rhodes/data=!4m7!3m6!1s0x888602052d900001:0x812bfb966f30bc6b!8m2!3d33.1539644!4d-87.5493003!16s%2Fg%2F11t9rrt867!19sChIJAQCQLQUChogRa7wwb5b7K4E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:47:10.761Z</t>
+  </si>
+  <si>
+    <t>Dr. Russell A. Lamoureux Sr, DMD</t>
+  </si>
+  <si>
+    <t>(205) 752-2531</t>
+  </si>
+  <si>
+    <t>610 Hargrove E Rd, Tuscaloosa, AL 35401</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Russell+A.+Lamoureux+Sr,+DMD/data=!4m7!3m6!1s0x88860286d93d34b3:0xd298725e463e1db5!8m2!3d33.1875532!4d-87.5273144!16s%2Fg%2F1tgfxd3z!19sChIJszQ92YYChogRtR0-Rl5ymNI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:47:12.956Z</t>
+  </si>
+  <si>
+    <t>Dr. John D. Marshall, DMD</t>
+  </si>
+  <si>
+    <t>(205) 339-6762</t>
+  </si>
+  <si>
+    <t>2820 Lurleen B Wallace Blvd, Northport, AL 35476</t>
+  </si>
+  <si>
+    <t>Northport</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+John+D.+Marshall,+DMD/data=!4m7!3m6!1s0x88861d2adde859df:0xf1b18d7bf12a272d!8m2!3d33.2366217!4d-87.5770244!16s%2Fg%2F1tp08w_c!19sChIJ31no3SodhogRLScq8XuNsfE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:47:28.450Z</t>
+  </si>
+  <si>
+    <t>Burgess, J Barry DMD</t>
+  </si>
+  <si>
+    <t>(205) 758-0846</t>
+  </si>
+  <si>
+    <t>221 Rice Mine Rd NE Ste a, Tuscaloosa, AL 35406</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Burgess,+J+Barry+DMD/data=!4m7!3m6!1s0x8888a805d0555d9d:0xc38cb3ffb0478b2e!8m2!3d33.228302!4d-87.5318994!16s%2Fg%2F1vsps7zw!19sChIJnV1V0AWoiIgRLotHsP-zjMM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:47:30.384Z</t>
+  </si>
+  <si>
+    <t>Dr. Matthew R. McCracken, DMD</t>
+  </si>
+  <si>
+    <t>(205) 556-6511</t>
+  </si>
+  <si>
+    <t>1402 Veterans Memorial Pkwy B, Tuscaloosa, AL 35404</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Matthew+R.+McCracken,+DMD/data=!4m7!3m6!1s0x8888a848fff97851:0xacea0c36785fa67a!8m2!3d33.197655!4d-87.51731!16s%2Fg%2F1tfczl2x!19sChIJUXj5_0ioiIgReqZfeDYM6qw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:47:32.736Z</t>
+  </si>
+  <si>
+    <t>Anderson Complete Dentistry</t>
+  </si>
+  <si>
+    <t>(205) 758-4721</t>
+  </si>
+  <si>
+    <t>204 McFarland Cir N, Tuscaloosa, AL 35406</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Anderson+Complete+Dentistry/data=!4m7!3m6!1s0x8888a8008939eb3f:0x4d1da7333a3df8be!8m2!3d33.233562!4d-87.536847!16s%2Fg%2F1tf5q_k0!19sChIJP-s5iQCoiIgRvvg9OjOnHU0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:48:27.026Z</t>
+  </si>
+  <si>
+    <t>Richard A Simpson, DMD</t>
+  </si>
+  <si>
+    <t>(205) 758-3341</t>
+  </si>
+  <si>
+    <t>1825 McFarland N Blvd, Tuscaloosa, AL 35406</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Richard+A+Simpson,+DMD/data=!4m7!3m6!1s0x88861d4d6f69af93:0xf90b059c60462963!8m2!3d33.2365922!4d-87.5496567!16s%2Fg%2F1tfk0m4d!19sChIJk69pb00dhogRYylGYJwFC_k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:49:12.878Z</t>
+  </si>
+  <si>
+    <t>Atkinson Scott E DDS</t>
+  </si>
+  <si>
+    <t>(205) 553-1523</t>
+  </si>
+  <si>
+    <t>621 Helen Keller Blvd #200, Tuscaloosa, AL 35404</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>SundayClosed; Monday8 AM–5 PM; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; Friday8 AM–5 PM; SaturdayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Atkinson+Scott+E+DDS/data=!4m7!3m6!1s0x8888a81551154b65:0xf3eb7fa62d9d284b!8m2!3d33.2119759!4d-87.5203295!16s%2Fg%2F1tg826x1!19sChIJZUsVURWoiIgRSyidLaZ_6_M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:49:25.529Z</t>
+  </si>
+  <si>
+    <t>Dr. Maxwell Moody III, DDS</t>
+  </si>
+  <si>
+    <t>(205) 349-3150</t>
+  </si>
+  <si>
+    <t>400 Hargrove E Rd, Tuscaloosa, AL 35401</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Maxwell+Moody+III,+DDS/data=!4m7!3m6!1s0x8888a9d2c1463d6f:0x7784a397e052b164!8m2!3d33.1883686!4d-87.5311665!16s%2Fg%2F1tdmwcxs!19sChIJbz1GwdKpiIgRZLFS4JejhHc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:49:37.227Z</t>
+  </si>
+  <si>
+    <t>Wright William E DDS</t>
+  </si>
+  <si>
+    <t>(205) 759-2811</t>
+  </si>
+  <si>
+    <t>Government office</t>
+  </si>
+  <si>
+    <t>6541 Alabama Hwy 69 S b, Tuscaloosa, AL 35405</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Wright+William+E+DDS/data=!4m7!3m6!1s0x88860203d4432559:0x262990be9dbc0995!8m2!3d33.1478518!4d-87.5447053!16s%2Fg%2F1td0tnl2!19sChIJWSVD1AMChogRlQm8nb6QKSY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:50:01.632Z</t>
   </si>
 </sst>
 </file>
@@ -1759,7 +1942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -5015,6 +5198,457 @@
         <v>455</v>
       </c>
     </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>456</v>
+      </c>
+      <c r="B80" t="s">
+        <v>457</v>
+      </c>
+      <c r="C80" t="s">
+        <v>36</v>
+      </c>
+      <c r="D80" t="s">
+        <v>458</v>
+      </c>
+      <c r="E80" t="s">
+        <v>459</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" t="s">
+        <v>71</v>
+      </c>
+      <c r="I80" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s">
+        <v>22</v>
+      </c>
+      <c r="K80" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" t="s">
+        <v>460</v>
+      </c>
+      <c r="M80" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>462</v>
+      </c>
+      <c r="B81" t="s">
+        <v>463</v>
+      </c>
+      <c r="C81" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" t="s">
+        <v>464</v>
+      </c>
+      <c r="E81" t="s">
+        <v>459</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s">
+        <v>38</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" t="s">
+        <v>465</v>
+      </c>
+      <c r="M81" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>467</v>
+      </c>
+      <c r="B82" t="s">
+        <v>468</v>
+      </c>
+      <c r="C82" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" t="s">
+        <v>469</v>
+      </c>
+      <c r="E82" t="s">
+        <v>459</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
+        <v>20</v>
+      </c>
+      <c r="I82" t="s">
+        <v>21</v>
+      </c>
+      <c r="J82" t="s">
+        <v>38</v>
+      </c>
+      <c r="K82" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" t="s">
+        <v>470</v>
+      </c>
+      <c r="M82" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>472</v>
+      </c>
+      <c r="B83" t="s">
+        <v>473</v>
+      </c>
+      <c r="C83" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" t="s">
+        <v>474</v>
+      </c>
+      <c r="E83" t="s">
+        <v>475</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" t="s">
+        <v>21</v>
+      </c>
+      <c r="J83" t="s">
+        <v>22</v>
+      </c>
+      <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" t="s">
+        <v>476</v>
+      </c>
+      <c r="M83" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>478</v>
+      </c>
+      <c r="B84" t="s">
+        <v>479</v>
+      </c>
+      <c r="C84" t="s">
+        <v>143</v>
+      </c>
+      <c r="D84" t="s">
+        <v>480</v>
+      </c>
+      <c r="E84" t="s">
+        <v>459</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" t="s">
+        <v>232</v>
+      </c>
+      <c r="I84" t="s">
+        <v>21</v>
+      </c>
+      <c r="J84" t="s">
+        <v>22</v>
+      </c>
+      <c r="K84" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" t="s">
+        <v>481</v>
+      </c>
+      <c r="M84" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>483</v>
+      </c>
+      <c r="B85" t="s">
+        <v>484</v>
+      </c>
+      <c r="C85" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" t="s">
+        <v>485</v>
+      </c>
+      <c r="E85" t="s">
+        <v>459</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" t="s">
+        <v>20</v>
+      </c>
+      <c r="I85" t="s">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s">
+        <v>38</v>
+      </c>
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" t="s">
+        <v>486</v>
+      </c>
+      <c r="M85" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>488</v>
+      </c>
+      <c r="B86" t="s">
+        <v>489</v>
+      </c>
+      <c r="C86" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" t="s">
+        <v>490</v>
+      </c>
+      <c r="E86" t="s">
+        <v>459</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" t="s">
+        <v>59</v>
+      </c>
+      <c r="I86" t="s">
+        <v>21</v>
+      </c>
+      <c r="J86" t="s">
+        <v>38</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" t="s">
+        <v>491</v>
+      </c>
+      <c r="M86" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>493</v>
+      </c>
+      <c r="B87" t="s">
+        <v>494</v>
+      </c>
+      <c r="C87" t="s">
+        <v>143</v>
+      </c>
+      <c r="D87" t="s">
+        <v>495</v>
+      </c>
+      <c r="E87" t="s">
+        <v>459</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" t="s">
+        <v>20</v>
+      </c>
+      <c r="I87" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" t="s">
+        <v>22</v>
+      </c>
+      <c r="K87" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" t="s">
+        <v>496</v>
+      </c>
+      <c r="M87" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>498</v>
+      </c>
+      <c r="B88" t="s">
+        <v>499</v>
+      </c>
+      <c r="C88" t="s">
+        <v>82</v>
+      </c>
+      <c r="D88" t="s">
+        <v>500</v>
+      </c>
+      <c r="E88" t="s">
+        <v>459</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" t="s">
+        <v>71</v>
+      </c>
+      <c r="I88" t="s">
+        <v>501</v>
+      </c>
+      <c r="J88" t="s">
+        <v>502</v>
+      </c>
+      <c r="K88" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" t="s">
+        <v>503</v>
+      </c>
+      <c r="M88" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>505</v>
+      </c>
+      <c r="B89" t="s">
+        <v>506</v>
+      </c>
+      <c r="C89" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" t="s">
+        <v>507</v>
+      </c>
+      <c r="E89" t="s">
+        <v>459</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>19</v>
+      </c>
+      <c r="H89" t="s">
+        <v>232</v>
+      </c>
+      <c r="I89" t="s">
+        <v>21</v>
+      </c>
+      <c r="J89" t="s">
+        <v>38</v>
+      </c>
+      <c r="K89" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" t="s">
+        <v>508</v>
+      </c>
+      <c r="M89" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>510</v>
+      </c>
+      <c r="B90" t="s">
+        <v>511</v>
+      </c>
+      <c r="C90" t="s">
+        <v>512</v>
+      </c>
+      <c r="D90" t="s">
+        <v>513</v>
+      </c>
+      <c r="E90" t="s">
+        <v>459</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
+        <v>514</v>
+      </c>
+      <c r="I90" t="s">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s">
+        <v>38</v>
+      </c>
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" t="s">
+        <v>515</v>
+      </c>
+      <c r="M90" t="s">
+        <v>516</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
